--- a/demo/Attribute_Model_and_LOV.xlsx
+++ b/demo/Attribute_Model_and_LOV.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ERPItemNo</t>
+          <t>ERP Item Number</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Product Category_SubCategory Classification Reference</t>
+          <t>Category Classification ID</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PIM_Cat_Subcat_concat</t>
+          <t>Category and Subcategory</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ITEM TYPE</t>
+          <t>Item Type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Product Web Title_Calc</t>
+          <t>Product Web Title</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Features_And_Benefits_Calc (no longer in use)</t>
+          <t>Features and Benefits Summary (no longer in use)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ORMD_Flag</t>
+          <t>ORMD Flag</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>UN Number ID_Calc</t>
+          <t>UN Number ID</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>UN Number Description_Calc</t>
+          <t>UN Number Description</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Features_And_Benefits_Calc (no longer in use) - French</t>
+          <t>Features and Benefits Summary (no longer in use) - French</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CANADA Harmonized Tariff Code (HTS)</t>
+          <t>Canada Harmonized Tariff Code (HTS)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NEW RETURN</t>
+          <t>New Return</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BROKEN BUT SALEABLE RETURN</t>
+          <t>Broken but Saleable Return</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BROKEN/DEFECTIVE RETURN</t>
+          <t>Broken/Defective Return</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>LastUpdated</t>
+          <t>Last Updated</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
